--- a/pos_web_benchmark/results/Programming_Benchmark_Report.xlsx
+++ b/pos_web_benchmark/results/Programming_Benchmark_Report.xlsx
@@ -6648,7 +6648,7 @@
         <v>36638.61</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0</v>
+        <v>26215.71</v>
       </c>
       <c r="F10" s="12">
         <f>IF(D10&gt;0, (E10-D10)/D10, 0)</f>
@@ -6658,13 +6658,13 @@
         <v>2.77</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="I10" s="11" t="n">
         <v>5.39</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>0</v>
+        <v>11.08</v>
       </c>
       <c r="K10" s="13" t="n">
         <v>0</v>
@@ -6693,9 +6693,9 @@
         <v>380.33</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="12">
+        <v>541.4299999999999</v>
+      </c>
+      <c r="F11" s="17">
         <f>IF(D11&gt;0, (E11-D11)/D11, 0)</f>
         <v/>
       </c>
@@ -6703,13 +6703,13 @@
         <v>269.94</v>
       </c>
       <c r="H11" s="16" t="n">
-        <v>0</v>
+        <v>204.07</v>
       </c>
       <c r="I11" s="16" t="n">
         <v>538.8</v>
       </c>
       <c r="J11" s="16" t="n">
-        <v>0</v>
+        <v>527.11</v>
       </c>
       <c r="K11" s="18" t="n">
         <v>0</v>
@@ -6738,9 +6738,9 @@
         <v>335.06</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="12">
+        <v>483.7</v>
+      </c>
+      <c r="F12" s="17">
         <f>IF(D12&gt;0, (E12-D12)/D12, 0)</f>
         <v/>
       </c>
@@ -6748,13 +6748,13 @@
         <v>308</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0</v>
+        <v>229.72</v>
       </c>
       <c r="I12" s="11" t="n">
         <v>622.73</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>0</v>
+        <v>604.38</v>
       </c>
       <c r="K12" s="13" t="n">
         <v>0</v>
@@ -6783,9 +6783,9 @@
         <v>322.64</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="12">
+        <v>465.83</v>
+      </c>
+      <c r="F13" s="17">
         <f>IF(D13&gt;0, (E13-D13)/D13, 0)</f>
         <v/>
       </c>
@@ -6793,13 +6793,13 @@
         <v>318.17</v>
       </c>
       <c r="H13" s="16" t="n">
-        <v>0</v>
+        <v>233.46</v>
       </c>
       <c r="I13" s="16" t="n">
         <v>635.77</v>
       </c>
       <c r="J13" s="16" t="n">
-        <v>0</v>
+        <v>582.46</v>
       </c>
       <c r="K13" s="18" t="n">
         <v>0</v>
@@ -6828,7 +6828,7 @@
         <v>39576.21</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0</v>
+        <v>30251.2</v>
       </c>
       <c r="F14" s="12">
         <f>IF(D14&gt;0, (E14-D14)/D14, 0)</f>
@@ -6838,13 +6838,13 @@
         <v>13.75</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>0</v>
+        <v>17.61</v>
       </c>
       <c r="I14" s="11" t="n">
         <v>33.11</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>0</v>
+        <v>42.53</v>
       </c>
       <c r="K14" s="13" t="n">
         <v>0</v>
@@ -6873,9 +6873,9 @@
         <v>376.83</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="12">
+        <v>488.52</v>
+      </c>
+      <c r="F15" s="17">
         <f>IF(D15&gt;0, (E15-D15)/D15, 0)</f>
         <v/>
       </c>
@@ -6883,13 +6883,13 @@
         <v>1236.85</v>
       </c>
       <c r="H15" s="16" t="n">
-        <v>0</v>
+        <v>1086.85</v>
       </c>
       <c r="I15" s="16" t="n">
         <v>3309.27</v>
       </c>
       <c r="J15" s="16" t="n">
-        <v>0</v>
+        <v>2734.98</v>
       </c>
       <c r="K15" s="23" t="n">
         <v>3512</v>
@@ -6918,9 +6918,9 @@
         <v>331.77</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="12">
+        <v>431.14</v>
+      </c>
+      <c r="F16" s="17">
         <f>IF(D16&gt;0, (E16-D16)/D16, 0)</f>
         <v/>
       </c>
@@ -6928,19 +6928,19 @@
         <v>1542.16</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>0</v>
+        <v>1208.4</v>
       </c>
       <c r="I16" s="11" t="n">
         <v>4167.66</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>0</v>
+        <v>2943.01</v>
       </c>
       <c r="K16" s="23" t="n">
         <v>2199</v>
       </c>
-      <c r="L16" s="13" t="n">
-        <v>0</v>
+      <c r="L16" s="23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -6963,9 +6963,9 @@
         <v>320.66</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="12">
+        <v>417.34</v>
+      </c>
+      <c r="F17" s="17">
         <f>IF(D17&gt;0, (E17-D17)/D17, 0)</f>
         <v/>
       </c>
@@ -6973,13 +6973,13 @@
         <v>1551.29</v>
       </c>
       <c r="H17" s="16" t="n">
-        <v>0</v>
+        <v>1242.56</v>
       </c>
       <c r="I17" s="16" t="n">
         <v>4212</v>
       </c>
       <c r="J17" s="16" t="n">
-        <v>0</v>
+        <v>2985.51</v>
       </c>
       <c r="K17" s="23" t="n">
         <v>2271</v>
@@ -7008,7 +7008,7 @@
         <v>39078.32</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0</v>
+        <v>30531.29</v>
       </c>
       <c r="F18" s="12">
         <f>IF(D18&gt;0, (E18-D18)/D18, 0)</f>
@@ -7018,13 +7018,13 @@
         <v>59.39</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>0</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="I18" s="11" t="n">
         <v>159.05</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>0</v>
+        <v>205.45</v>
       </c>
       <c r="K18" s="13" t="n">
         <v>0</v>
@@ -7053,9 +7053,9 @@
         <v>369.87</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="12">
+        <v>466.54</v>
+      </c>
+      <c r="F19" s="17">
         <f>IF(D19&gt;0, (E19-D19)/D19, 0)</f>
         <v/>
       </c>
@@ -7063,19 +7063,19 @@
         <v>3429.49</v>
       </c>
       <c r="H19" s="16" t="n">
-        <v>0</v>
+        <v>3478.82</v>
       </c>
       <c r="I19" s="16" t="n">
         <v>7636.67</v>
       </c>
       <c r="J19" s="16" t="n">
-        <v>0</v>
+        <v>8576.43</v>
       </c>
       <c r="K19" s="23" t="n">
         <v>101476</v>
       </c>
-      <c r="L19" s="18" t="n">
-        <v>0</v>
+      <c r="L19" s="23" t="n">
+        <v>87452</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -7098,9 +7098,9 @@
         <v>323.33</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="12">
+        <v>411.65</v>
+      </c>
+      <c r="F20" s="17">
         <f>IF(D20&gt;0, (E20-D20)/D20, 0)</f>
         <v/>
       </c>
@@ -7108,19 +7108,19 @@
         <v>3618.49</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>0</v>
+        <v>3701.09</v>
       </c>
       <c r="I20" s="11" t="n">
         <v>7894.75</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>0</v>
+        <v>9018.07</v>
       </c>
       <c r="K20" s="23" t="n">
         <v>103331</v>
       </c>
-      <c r="L20" s="13" t="n">
-        <v>0</v>
+      <c r="L20" s="23" t="n">
+        <v>108215</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -7143,9 +7143,9 @@
         <v>310.65</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="12">
+        <v>397.68</v>
+      </c>
+      <c r="F21" s="17">
         <f>IF(D21&gt;0, (E21-D21)/D21, 0)</f>
         <v/>
       </c>
@@ -7153,19 +7153,19 @@
         <v>3841.22</v>
       </c>
       <c r="H21" s="16" t="n">
-        <v>0</v>
+        <v>3653.69</v>
       </c>
       <c r="I21" s="16" t="n">
         <v>7902.21</v>
       </c>
       <c r="J21" s="16" t="n">
-        <v>0</v>
+        <v>9048.959999999999</v>
       </c>
       <c r="K21" s="23" t="n">
         <v>98888</v>
       </c>
-      <c r="L21" s="18" t="n">
-        <v>0</v>
+      <c r="L21" s="23" t="n">
+        <v>119298</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -7188,7 +7188,7 @@
         <v>38702.9</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0</v>
+        <v>29814.67</v>
       </c>
       <c r="F22" s="12">
         <f>IF(D22&gt;0, (E22-D22)/D22, 0)</f>
@@ -7198,13 +7198,13 @@
         <v>274.61</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>0</v>
+        <v>361.09</v>
       </c>
       <c r="I22" s="11" t="n">
         <v>622.9</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>0</v>
+        <v>852.49</v>
       </c>
       <c r="K22" s="13" t="n">
         <v>0</v>
@@ -7233,9 +7233,9 @@
         <v>349.38</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="12">
+        <v>452.79</v>
+      </c>
+      <c r="F23" s="17">
         <f>IF(D23&gt;0, (E23-D23)/D23, 0)</f>
         <v/>
       </c>
@@ -7243,19 +7243,19 @@
         <v>5183.24</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>0</v>
+        <v>3924.78</v>
       </c>
       <c r="I23" s="16" t="n">
         <v>9217.120000000001</v>
       </c>
       <c r="J23" s="16" t="n">
-        <v>0</v>
+        <v>8992.940000000001</v>
       </c>
       <c r="K23" s="23" t="n">
         <v>1930412</v>
       </c>
-      <c r="L23" s="18" t="n">
-        <v>0</v>
+      <c r="L23" s="23" t="n">
+        <v>1057974</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
